--- a/public/db/SETOR.xlsx
+++ b/public/db/SETOR.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="206">
   <si>
     <t>CODIGO</t>
   </si>
@@ -625,6 +625,18 @@
   </si>
   <si>
     <t>0100</t>
+  </si>
+  <si>
+    <t>0101</t>
+  </si>
+  <si>
+    <t>SECADORA RESINA</t>
+  </si>
+  <si>
+    <t>0102</t>
+  </si>
+  <si>
+    <t>CAMINHAO BLX-8024 SP</t>
   </si>
 </sst>
 </file>
@@ -1953,6 +1965,22 @@
         <v>173</v>
       </c>
     </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A102" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A103" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C109" s="2"/>
     </row>
